--- a/data/xlsx/sbce_config_kvm_ems_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EMS" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="EMS" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -136,7 +136,7 @@
     <t xml:space="preserve">ip0</t>
   </si>
   <si>
-    <t xml:space="preserve">192.168.122.140</t>
+    <t xml:space="preserve">10.10.48.70</t>
   </si>
   <si>
     <t xml:space="preserve">Management IPv4 Address: (*) - The IPv4 address for the management interface.</t>
@@ -154,6 +154,9 @@
     <t xml:space="preserve">gateway</t>
   </si>
   <si>
+    <t xml:space="preserve">10.10.48.254</t>
+  </si>
+  <si>
     <t xml:space="preserve">Default gateway: (*) - The IPv4 gateway for the management interface.</t>
   </si>
   <si>
@@ -244,6 +247,9 @@
     <t xml:space="preserve">ntpservers</t>
   </si>
   <si>
+    <t xml:space="preserve">10.10.48.250</t>
+  </si>
+  <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
   </si>
   <si>
@@ -256,6 +262,9 @@
     <t xml:space="preserve">dns</t>
   </si>
   <si>
+    <t xml:space="preserve">10.10.48.92</t>
+  </si>
+  <si>
     <t xml:space="preserve">DNS Address: - The IPv4 address list for DNS servers.</t>
   </si>
   <si>
@@ -304,7 +313,7 @@
     <t xml:space="preserve">M1</t>
   </si>
   <si>
-    <t xml:space="preserve">virbr0</t>
+    <t xml:space="preserve">bridge48</t>
   </si>
   <si>
     <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
@@ -386,13 +395,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
@@ -411,6 +421,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -455,7 +471,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -464,8 +480,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -481,147 +505,147 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.25"/>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAEAEAE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -689,185 +713,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0e2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="e97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196b24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="a02b93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4ea72e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607d"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70.22"/>
@@ -1039,333 +891,333 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>4</v>
+      <c r="B16" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="0" t="str">
+        <v>55</v>
+      </c>
+      <c r="B21" s="4" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>ems.lab.local</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>4</v>
+        <v>74</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="0" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="0" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1537,7 +1389,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/data/xlsx/sbce_config_kvm_ems_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -136,7 +136,7 @@
     <t xml:space="preserve">ip0</t>
   </si>
   <si>
-    <t xml:space="preserve">10.10.48.70</t>
+    <t xml:space="preserve">10.10.10.10</t>
   </si>
   <si>
     <t xml:space="preserve">Management IPv4 Address: (*) - The IPv4 address for the management interface.</t>
@@ -154,7 +154,7 @@
     <t xml:space="preserve">gateway</t>
   </si>
   <si>
-    <t xml:space="preserve">10.10.48.254</t>
+    <t xml:space="preserve">10.10.10.1</t>
   </si>
   <si>
     <t xml:space="preserve">Default gateway: (*) - The IPv4 gateway for the management interface.</t>
@@ -247,9 +247,6 @@
     <t xml:space="preserve">ntpservers</t>
   </si>
   <si>
-    <t xml:space="preserve">10.10.48.250</t>
-  </si>
-  <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
   </si>
   <si>
@@ -262,9 +259,6 @@
     <t xml:space="preserve">dns</t>
   </si>
   <si>
-    <t xml:space="preserve">10.10.48.92</t>
-  </si>
-  <si>
     <t xml:space="preserve">DNS Address: - The IPv4 address list for DNS servers.</t>
   </si>
   <si>
@@ -313,7 +307,7 @@
     <t xml:space="preserve">M1</t>
   </si>
   <si>
-    <t xml:space="preserve">bridge48</t>
+    <t xml:space="preserve">lab</t>
   </si>
   <si>
     <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
@@ -719,7 +713,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70.22"/>
@@ -1022,202 +1016,202 @@
       <c r="A28" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="0" t="s">
         <v>77</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="0" t="s">
         <v>79</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="0" t="s">
         <v>86</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="0" t="s">
         <v>96</v>
-      </c>
-      <c r="B37" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="0" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/xlsx/sbce_config_kvm_ems_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EMS" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="EMS" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="120">
   <si>
     <t xml:space="preserve">platform_type</t>
   </si>
@@ -305,9 +305,6 @@
   </si>
   <si>
     <t xml:space="preserve">M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lab</t>
   </si>
   <si>
     <t xml:space="preserve">M1 NIC Port-group / Bridge name</t>
@@ -389,11 +386,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -415,12 +411,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -465,25 +455,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -707,511 +693,617 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="70.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="108.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B21" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(B9, ".", B20)</f>
         <v>ems.lab.local</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="0" t="s">
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="B38" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="0" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="0" t="s">
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="0" t="s">
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="0" t="s">
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C42" s="0" t="s">
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="0" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="C44" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C44" s="0" t="s">
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="C45" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="0" t="s">
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="C46" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C46" s="0" t="s">
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="C47" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C47" s="0" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="B48" s="2"/>
+      <c r="C48" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="0" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="B49" s="2"/>
+      <c r="C49" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="0" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1383,7 +1475,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/data/xlsx/sbce_config_kvm_ems_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_template.xlsx
@@ -244,7 +244,7 @@
     <t xml:space="preserve">Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
   <si>
-    <t xml:space="preserve">ntpservers</t>
+    <t xml:space="preserve">ntpserver</t>
   </si>
   <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
@@ -389,11 +389,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -411,6 +411,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -455,20 +462,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -805,47 +808,47 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="70.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.78"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -856,18 +859,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -878,7 +881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -889,18 +892,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -911,62 +914,62 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
@@ -977,18 +980,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -996,18 +999,18 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
@@ -1038,62 +1041,62 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>71</v>
       </c>
@@ -1104,18 +1107,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>76</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>78</v>
       </c>
@@ -1134,7 +1137,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>80</v>
       </c>
@@ -1142,7 +1145,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>82</v>
       </c>
@@ -1150,51 +1153,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>88</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>94</v>
       </c>
@@ -1205,7 +1208,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>96</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>98</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>100</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>102</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>104</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>106</v>
       </c>
@@ -1256,7 +1259,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>108</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>110</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>112</v>
       </c>
@@ -1280,7 +1283,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>114</v>
       </c>
@@ -1288,20 +1291,18 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B48" s="2"/>
       <c r="C48" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B49" s="2"/>
       <c r="C49" s="1" t="s">
         <v>119</v>
       </c>
@@ -1412,71 +1413,91 @@
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="15">
+  <dataValidations count="20">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
+      <formula1>"ESXI,KVM"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
+      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
+      <formula1>21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
+      <formula1>"primary,secondary"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B14" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
+      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" promptTitle="Host IP or FQDN" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B3" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31:B32" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
+      <formula1>7</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
+      <formula1>8</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
+      <formula1>"A1,A2,B1,B2"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B48:B49" type="none">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
+      <formula1>$B$1="ESXI"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B50" type="custom">
+      <formula1>$B$10&lt;&gt;"EMS"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B8" type="list">
       <formula1>"DUAL_STACK,IPV4"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B11" type="textLength">
-      <formula1>21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B1" type="list">
-      <formula1>"ESXI,KVM"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B10" type="list">
-      <formula1>"EMS+SBCE,SBCE,EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B13" type="list">
-      <formula1>"primary,secondary"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B45" type="list">
-      <formula1>"A1,A2,B1,B2"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>$B$1="ESXI"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS+SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>$B$10&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47 B50" type="custom">
-      <formula1>$B$10&lt;&gt;"EMS"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>$B$10="SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B33:B35" type="textLength">
-      <formula1>7</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B36" type="textLength">
-      <formula1>8</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
